--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,137 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121994465</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57315</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Järna gård, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>610120</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557108</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ugglan hoade nere från ravinen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Monica Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Monica Larsson, Peter Lund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>121994465</v>
       </c>
       <c r="B5" t="n">
-        <v>57315</v>
+        <v>57323</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>121994465</v>
       </c>
       <c r="B5" t="n">
-        <v>57323</v>
+        <v>57327</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>115598504</v>
       </c>
       <c r="B3" t="n">
-        <v>57315</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>121994465</v>
       </c>
       <c r="B5" t="n">
-        <v>57332</v>
+        <v>57337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -813,11 +813,6 @@
       <c r="E3" t="n">
         <v>102622</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pärluggla</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Aegolius funereus</t>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>115598504</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,6 +812,11 @@
       </c>
       <c r="E3" t="n">
         <v>102622</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>115598504</v>
       </c>
       <c r="B3" t="n">
-        <v>57324</v>
+        <v>57325</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>123576606</v>
       </c>
       <c r="B6" t="n">
-        <v>56590</v>
+        <v>56596</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>123576606</v>
       </c>
       <c r="B6" t="n">
-        <v>56596</v>
+        <v>56599</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115598774</v>
+        <v>121994465</v>
       </c>
       <c r="B4" t="n">
-        <v>57181</v>
+        <v>57337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>102975</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,15 +950,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,22 +996,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ugglan hoade nere från ravinen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,6 +1027,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121994465</v>
+        <v>123576606</v>
       </c>
       <c r="B5" t="n">
-        <v>57337</v>
+        <v>56599</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,25 +1060,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102975</v>
+        <v>102932</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1077,24 +1086,39 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Järna gård, Srm</t>
+          <t>Oxhagens viltvatten, järna gård, Srm, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610120</v>
+        <v>610162</v>
       </c>
       <c r="R5" t="n">
-        <v>6557108</v>
+        <v>6557113</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,27 +1142,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ugglan hoade nere från ravinen</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,11 +1169,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1163,146 +1177,10 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monica Larsson, Peter Lund</t>
+          <t>Peter Lund, Monica Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>123576606</v>
-      </c>
-      <c r="B6" t="n">
-        <v>56599</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>102932</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kricka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Anas crecca</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Oxhagens viltvatten, järna gård, Srm, Srm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>610162</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6557113</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Gnesta</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Gryt</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Monica Larsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Monica Larsson, Peter Lund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52828-2020 artfynd.xlsx
+++ b/artfynd/A 52828-2020 artfynd.xlsx
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Lund, Monica Larsson</t>
+          <t>Monica Larsson, Peter Lund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
